--- a/r4-JoanneumResearch-PreNUDGE-AppData-physical_activity/observations-summary.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-physical_activity/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="69">
   <si>
     <t>Profile</t>
   </si>
@@ -74,6 +74,45 @@
     <t>CodeableConcept</t>
   </si>
   <si>
+    <t>at-prenudge-bmi-observation</t>
+  </si>
+  <si>
+    <t>AT PreNUDGE Observation Body Mass Index</t>
+  </si>
+  <si>
+    <t>Observation Category Codes#vital-signs</t>
+  </si>
+  <si>
+    <t>LOINC#39156-5</t>
+  </si>
+  <si>
+    <t>at-prenudge-bodyheight-observation</t>
+  </si>
+  <si>
+    <t>AT PreNUDGE Observation Body Height</t>
+  </si>
+  <si>
+    <t>LOINC#8302-2</t>
+  </si>
+  <si>
+    <t>at-prenudge-bodyweight-observation</t>
+  </si>
+  <si>
+    <t>AT PreNUDGE Observation Body Weight</t>
+  </si>
+  <si>
+    <t>LOINC#29463-7</t>
+  </si>
+  <si>
+    <t>at-prenudge-education-observation</t>
+  </si>
+  <si>
+    <t>AT PreNUDGE Observation Highest Completed Education</t>
+  </si>
+  <si>
+    <t>LOINC#82589-3</t>
+  </si>
+  <si>
     <t>at-prenudge-muscle-strengthening-observation</t>
   </si>
   <si>
@@ -162,6 +201,24 @@
   </si>
   <si>
     <t>SNOMED CT#276339004</t>
+  </si>
+  <si>
+    <t>at-prenudge-work-soc-score-observation</t>
+  </si>
+  <si>
+    <t>AT PreNUDGE Observation Work-SoC Category Score</t>
+  </si>
+  <si>
+    <t>AT PreNUDGE Workability Codes#work-soc-category-score</t>
+  </si>
+  <si>
+    <t>AT PreNUDGE Workability Codes#work-soc-comprehensibility</t>
+  </si>
+  <si>
+    <t>AT PreNUDGE Workability Codes#work-soc-manageability</t>
+  </si>
+  <si>
+    <t>AT PreNUDGE Workability Codes#work-soc-meaningfulness</t>
   </si>
 </sst>
 </file>
@@ -295,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:K27"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -411,13 +468,13 @@
         <v>21</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D4" t="s" s="2">
         <v>13</v>
       </c>
       <c r="E4" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F4" t="s" s="2">
         <v>13</v>
@@ -440,19 +497,19 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D5" t="s" s="2">
         <v>13</v>
       </c>
       <c r="E5" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F5" t="s" s="2">
         <v>13</v>
@@ -461,7 +518,7 @@
         <v>15</v>
       </c>
       <c r="H5" t="s" s="2">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="I5" t="s" s="2">
         <v>17</v>
@@ -475,25 +532,25 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C6" t="s" s="2">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D6" t="s" s="2">
         <v>13</v>
       </c>
       <c r="E6" t="s" s="2">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F6" t="s" s="2">
         <v>13</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>16</v>
@@ -510,10 +567,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C7" t="s" s="2">
         <v>13</v>
@@ -522,16 +579,16 @@
         <v>13</v>
       </c>
       <c r="E7" t="s" s="2">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F7" t="s" s="2">
         <v>13</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H7" t="s" s="2">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I7" t="s" s="2">
         <v>17</v>
@@ -545,10 +602,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="C8" t="s" s="2">
         <v>13</v>
@@ -557,13 +614,13 @@
         <v>13</v>
       </c>
       <c r="E8" t="s" s="2">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="F8" t="s" s="2">
         <v>13</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>16</v>
@@ -580,10 +637,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="C9" t="s" s="2">
         <v>13</v>
@@ -592,16 +649,16 @@
         <v>13</v>
       </c>
       <c r="E9" t="s" s="2">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="F9" t="s" s="2">
         <v>13</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H9" t="s" s="2">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="I9" t="s" s="2">
         <v>17</v>
@@ -615,10 +672,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="C10" t="s" s="2">
         <v>13</v>
@@ -627,13 +684,13 @@
         <v>13</v>
       </c>
       <c r="E10" t="s" s="2">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="F10" t="s" s="2">
         <v>13</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>16</v>
@@ -650,10 +707,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C11" t="s" s="2">
         <v>13</v>
@@ -662,13 +719,13 @@
         <v>13</v>
       </c>
       <c r="E11" t="s" s="2">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="F11" t="s" s="2">
         <v>13</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>16</v>
@@ -685,7 +742,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="B12" t="s" s="2">
         <v>37</v>
@@ -703,10 +760,10 @@
         <v>13</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="I12" t="s" s="2">
         <v>17</v>
@@ -720,10 +777,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C13" t="s" s="2">
         <v>13</v>
@@ -732,16 +789,16 @@
         <v>13</v>
       </c>
       <c r="E13" t="s" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F13" t="s" s="2">
         <v>13</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I13" t="s" s="2">
         <v>17</v>
@@ -755,10 +812,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C14" t="s" s="2">
         <v>13</v>
@@ -767,7 +824,7 @@
         <v>13</v>
       </c>
       <c r="E14" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F14" t="s" s="2">
         <v>13</v>
@@ -776,7 +833,7 @@
         <v>15</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I14" t="s" s="2">
         <v>17</v>
@@ -790,10 +847,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C15" t="s" s="2">
         <v>13</v>
@@ -802,13 +859,13 @@
         <v>13</v>
       </c>
       <c r="E15" t="s" s="2">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F15" t="s" s="2">
         <v>13</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>16</v>
@@ -825,10 +882,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="C16" t="s" s="2">
         <v>13</v>
@@ -837,16 +894,16 @@
         <v>13</v>
       </c>
       <c r="E16" t="s" s="2">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="F16" t="s" s="2">
         <v>13</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>17</v>
@@ -860,10 +917,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>13</v>
+        <v>52</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="C17" t="s" s="2">
         <v>13</v>
@@ -872,13 +929,13 @@
         <v>13</v>
       </c>
       <c r="E17" t="s" s="2">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="F17" t="s" s="2">
         <v>13</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>16</v>
@@ -895,10 +952,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>13</v>
+        <v>55</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="C18" t="s" s="2">
         <v>13</v>
@@ -907,16 +964,16 @@
         <v>13</v>
       </c>
       <c r="E18" t="s" s="2">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="F18" t="s" s="2">
         <v>13</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>17</v>
@@ -933,7 +990,7 @@
         <v>13</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="C19" t="s" s="2">
         <v>13</v>
@@ -942,7 +999,7 @@
         <v>13</v>
       </c>
       <c r="E19" t="s" s="2">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="F19" t="s" s="2">
         <v>13</v>
@@ -960,6 +1017,286 @@
         <v>13</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="C20" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D20" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E20" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="F20" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G20" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H20" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I20" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J20" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K20" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B21" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="C21" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D21" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E21" t="s" s="2">
+        <v>60</v>
+      </c>
+      <c r="F21" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G21" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H21" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I21" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J21" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K21" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B22" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="C22" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D22" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E22" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="F22" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G22" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H22" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I22" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J22" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K22" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B23" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="C23" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D23" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E23" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="F23" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G23" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H23" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I23" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J23" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K23" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="B24" t="s" s="2">
+        <v>64</v>
+      </c>
+      <c r="C24" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D24" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E24" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="F24" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G24" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="H24" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="I24" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J24" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K24" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B25" t="s" s="2">
+        <v>64</v>
+      </c>
+      <c r="C25" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D25" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E25" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="F25" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G25" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H25" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I25" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J25" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K25" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B26" t="s" s="2">
+        <v>64</v>
+      </c>
+      <c r="C26" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D26" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E26" t="s" s="2">
+        <v>67</v>
+      </c>
+      <c r="F26" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G26" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H26" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I26" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J26" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K26" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B27" t="s" s="2">
+        <v>64</v>
+      </c>
+      <c r="C27" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D27" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E27" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="F27" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G27" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H27" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I27" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J27" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K27" t="s" s="2">
         <v>13</v>
       </c>
     </row>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-physical_activity/observations-summary.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-physical_activity/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="78">
   <si>
     <t>Profile</t>
   </si>
@@ -120,6 +120,33 @@
   </si>
   <si>
     <t>LOINC#82291-6</t>
+  </si>
+  <si>
+    <t>at-prenudge-nutrition-fruitportions-observation</t>
+  </si>
+  <si>
+    <t>AT PreNUDGE Observation Nutrition Fruit Portions</t>
+  </si>
+  <si>
+    <t>LOINC#89765-5</t>
+  </si>
+  <si>
+    <t>at-prenudge-nutrition-sugarsalty-observation</t>
+  </si>
+  <si>
+    <t>AT PreNUDGE Observation Nutrition Sugar Salty Frequency</t>
+  </si>
+  <si>
+    <t>SNOMED CT#364395008</t>
+  </si>
+  <si>
+    <t>at-prenudge-nutrition-vegetableportions-observation</t>
+  </si>
+  <si>
+    <t>AT PreNUDGE Observation Nutrition Vegetable Portions</t>
+  </si>
+  <si>
+    <t>LOINC#89764-8</t>
   </si>
   <si>
     <t>at-prenudge-physical-activity-minutes-observation</t>
@@ -352,7 +379,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K27"/>
+  <dimension ref="A1:K30"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -658,7 +685,7 @@
         <v>15</v>
       </c>
       <c r="H9" t="s" s="2">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="I9" t="s" s="2">
         <v>17</v>
@@ -672,10 +699,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C10" t="s" s="2">
         <v>13</v>
@@ -684,16 +711,16 @@
         <v>13</v>
       </c>
       <c r="E10" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F10" t="s" s="2">
         <v>13</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I10" t="s" s="2">
         <v>17</v>
@@ -707,10 +734,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C11" t="s" s="2">
         <v>13</v>
@@ -719,13 +746,13 @@
         <v>13</v>
       </c>
       <c r="E11" t="s" s="2">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F11" t="s" s="2">
         <v>13</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>16</v>
@@ -742,10 +769,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="C12" t="s" s="2">
         <v>13</v>
@@ -754,16 +781,16 @@
         <v>13</v>
       </c>
       <c r="E12" t="s" s="2">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="F12" t="s" s="2">
         <v>13</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="I12" t="s" s="2">
         <v>17</v>
@@ -780,7 +807,7 @@
         <v>13</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="C13" t="s" s="2">
         <v>13</v>
@@ -789,7 +816,7 @@
         <v>13</v>
       </c>
       <c r="E13" t="s" s="2">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="F13" t="s" s="2">
         <v>13</v>
@@ -798,7 +825,7 @@
         <v>13</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="I13" t="s" s="2">
         <v>17</v>
@@ -812,10 +839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>43</v>
+        <v>13</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C14" t="s" s="2">
         <v>13</v>
@@ -824,13 +851,13 @@
         <v>13</v>
       </c>
       <c r="E14" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="F14" t="s" s="2">
         <v>13</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>16</v>
@@ -847,25 +874,25 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B15" t="s" s="2">
         <v>46</v>
       </c>
-      <c r="B15" t="s" s="2">
+      <c r="C15" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D15" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E15" t="s" s="2">
         <v>47</v>
       </c>
-      <c r="C15" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D15" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E15" t="s" s="2">
-        <v>48</v>
-      </c>
       <c r="F15" t="s" s="2">
         <v>13</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>16</v>
@@ -882,10 +909,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C16" t="s" s="2">
         <v>13</v>
@@ -900,7 +927,7 @@
         <v>13</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>19</v>
@@ -973,7 +1000,7 @@
         <v>15</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>17</v>
@@ -987,10 +1014,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>13</v>
+        <v>58</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C19" t="s" s="2">
         <v>13</v>
@@ -999,16 +1026,16 @@
         <v>13</v>
       </c>
       <c r="E19" t="s" s="2">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F19" t="s" s="2">
         <v>13</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>17</v>
@@ -1022,10 +1049,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>13</v>
+        <v>61</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="C20" t="s" s="2">
         <v>13</v>
@@ -1034,13 +1061,13 @@
         <v>13</v>
       </c>
       <c r="E20" t="s" s="2">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="F20" t="s" s="2">
         <v>13</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>16</v>
@@ -1057,10 +1084,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>13</v>
+        <v>64</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="C21" t="s" s="2">
         <v>13</v>
@@ -1069,16 +1096,16 @@
         <v>13</v>
       </c>
       <c r="E21" t="s" s="2">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F21" t="s" s="2">
         <v>13</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>17</v>
@@ -1095,7 +1122,7 @@
         <v>13</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="C22" t="s" s="2">
         <v>13</v>
@@ -1104,7 +1131,7 @@
         <v>13</v>
       </c>
       <c r="E22" t="s" s="2">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="F22" t="s" s="2">
         <v>13</v>
@@ -1130,7 +1157,7 @@
         <v>13</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="C23" t="s" s="2">
         <v>13</v>
@@ -1139,7 +1166,7 @@
         <v>13</v>
       </c>
       <c r="E23" t="s" s="2">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="F23" t="s" s="2">
         <v>13</v>
@@ -1162,10 +1189,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>63</v>
+        <v>13</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C24" t="s" s="2">
         <v>13</v>
@@ -1174,16 +1201,16 @@
         <v>13</v>
       </c>
       <c r="E24" t="s" s="2">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="F24" t="s" s="2">
         <v>13</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>17</v>
@@ -1200,7 +1227,7 @@
         <v>13</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C25" t="s" s="2">
         <v>13</v>
@@ -1209,7 +1236,7 @@
         <v>13</v>
       </c>
       <c r="E25" t="s" s="2">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F25" t="s" s="2">
         <v>13</v>
@@ -1235,7 +1262,7 @@
         <v>13</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C26" t="s" s="2">
         <v>13</v>
@@ -1244,7 +1271,7 @@
         <v>13</v>
       </c>
       <c r="E26" t="s" s="2">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="F26" t="s" s="2">
         <v>13</v>
@@ -1267,10 +1294,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>13</v>
+        <v>72</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="C27" t="s" s="2">
         <v>13</v>
@@ -1279,16 +1306,16 @@
         <v>13</v>
       </c>
       <c r="E27" t="s" s="2">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="F27" t="s" s="2">
         <v>13</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>17</v>
@@ -1297,6 +1324,111 @@
         <v>13</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="C28" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D28" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E28" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="F28" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G28" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H28" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I28" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J28" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K28" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="C29" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D29" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E29" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="F29" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G29" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H29" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I29" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J29" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K29" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="C30" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D30" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="F30" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G30" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H30" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I30" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J30" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K30" t="s" s="2">
         <v>13</v>
       </c>
     </row>
